--- a/dcf/GTLB.xlsx
+++ b/dcf/GTLB.xlsx
@@ -361,127 +361,127 @@
   <commentList>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B21" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C21" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B22" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C22" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B23" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C23" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B24" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C24" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B25" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C25" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>builder default — last-year capex +10% unless set to guidance; edits not tracked</t>
+        <t>workbook (synced) — last-year capex +10% unless set to guidance; edits not tracked</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>Opus: 22.0x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C52" authorId="0" shapeId="0">
@@ -917,7 +917,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>builder defaults (consensus-anchored; no Opus pass)</t>
+          <t>Opus 4.8 — values as of 2026-07-06 (provenance seeded)</t>
         </is>
       </c>
     </row>
@@ -1172,184 +1172,184 @@
     </row>
     <row r="5">
       <c r="A5" s="52" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>10.89546548989397</v>
+        <v>15.12182549226876</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>10.70849228542792</v>
+        <v>14.74146659406419</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>10.5311737322449</v>
+        <v>14.38045149220296</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>10.36298183371309</v>
+        <v>14.03772501504744</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>10.20341954980526</v>
+        <v>13.71229388006082</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>10.05201885435368</v>
+        <v>13.4032228052653</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>9.90833892230752</v>
+        <v>13.10963088125687</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>11.31810149013145</v>
+        <v>15.54446149250624</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>11.11178971629154</v>
+        <v>15.14476402492781</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>10.9161015082407</v>
+        <v>14.76537926819877</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>10.73045615184652</v>
+        <v>14.40519933318088</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>10.55430698283082</v>
+        <v>14.06318131308638</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>10.38713924944484</v>
+        <v>13.73834320035646</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>10.22846811820246</v>
+        <v>13.4297600771518</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>11.74073749036892</v>
+        <v>15.96709749274372</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>11.51508714715517</v>
+        <v>15.54806145579144</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>11.30102928423651</v>
+        <v>15.15030704419457</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>11.09793046997996</v>
+        <v>14.77267365131432</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>10.90519441585638</v>
+        <v>14.41406874611193</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>10.722259644536</v>
+        <v>14.07346359544762</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>10.54859731409739</v>
+        <v>13.74988927304674</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>12.1633734906064</v>
+        <v>16.3897334929812</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>11.9183845780188</v>
+        <v>15.95135888665507</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>11.68595706023232</v>
+        <v>15.53523482019038</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>11.46540478811339</v>
+        <v>15.14014796944775</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>11.25608184888193</v>
+        <v>14.76495617913749</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>11.05738003962716</v>
+        <v>14.40858399053878</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>10.86872650999232</v>
+        <v>14.07001846894167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>12.58600949084388</v>
+        <v>16.81236949321868</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>12.32168200888242</v>
+        <v>16.35465631751869</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>12.07088483622812</v>
+        <v>15.92016259618618</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>11.83287910624683</v>
+        <v>15.50762228758119</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>11.60696928190749</v>
+        <v>15.11584361216304</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>11.39250043471832</v>
+        <v>14.74370438562994</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>11.18885570588726</v>
+        <v>14.3901476648366</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>13.00864549108137</v>
+        <v>17.23500549345616</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>12.72497943974605</v>
+        <v>16.75795374838232</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>12.45581261222393</v>
+        <v>16.30509037218199</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>12.20035342438026</v>
+        <v>15.87509660571462</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>11.95785671493304</v>
+        <v>15.4667310451886</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>11.72762082980949</v>
+        <v>15.0788247807211</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>11.50898490178219</v>
+        <v>14.71027686073154</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>13.43128149131884</v>
+        <v>17.65764149369364</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>13.12827687060968</v>
+        <v>17.16125117924595</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>12.84074038821973</v>
+        <v>16.6900181481778</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>12.5678277425137</v>
+        <v>16.24257092384806</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>12.3087441479586</v>
+        <v>15.81761847821416</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>12.06274122490065</v>
+        <v>15.41394517581227</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>11.82911409767713</v>
+        <v>15.03040605662648</v>
       </c>
     </row>
     <row r="13">
@@ -1372,7 +1372,7 @@
         <v>0.080035</v>
       </c>
       <c r="C14" s="56" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.3986756795380549</v>
+        <v>0.3512926050206785</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24499,7 +24499,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -24696,13 +24696,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>11.46540478811339</v>
+        <v>15.14014796944775</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>17.31260582596765</v>
+        <v>23.64937247133113</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>7.724187401051713</v>
+        <v>9.459963066721421</v>
       </c>
     </row>
     <row r="59">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no Opus assumptions file — every input is a builder default</t>
+          <t>seeded 2026-07-06 from the synced assumptions block (pass predates provenance tracking — may already include your edits)</t>
         </is>
       </c>
     </row>
@@ -24928,7 +24928,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24936,7 +24936,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="31" t="inlineStr"/>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24955,7 +24959,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24963,7 +24967,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr"/>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24982,7 +24990,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -24990,7 +24998,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr"/>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25009,7 +25021,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -25017,7 +25029,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25036,7 +25052,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -25044,7 +25060,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr"/>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25063,7 +25083,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -25071,7 +25091,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr"/>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25090,7 +25114,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -25098,7 +25122,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr"/>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25117,7 +25145,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -25125,7 +25153,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr"/>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25144,7 +25176,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -25152,7 +25184,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr"/>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25171,7 +25207,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -25179,7 +25215,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr"/>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25198,7 +25238,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -25206,7 +25246,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr"/>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25225,7 +25269,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -25233,7 +25277,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr"/>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25252,7 +25300,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -25260,7 +25308,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="31" t="inlineStr"/>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -25279,7 +25331,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -25287,7 +25339,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr"/>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25306,7 +25362,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -25314,7 +25370,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="31" t="inlineStr"/>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25333,7 +25393,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -25341,7 +25401,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="31" t="inlineStr"/>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25360,7 +25424,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -25368,7 +25432,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="31" t="inlineStr"/>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25387,7 +25455,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -25395,7 +25463,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="31" t="inlineStr"/>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -25414,7 +25486,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -25422,7 +25494,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="31" t="inlineStr"/>
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -25441,7 +25517,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -25449,7 +25525,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F27" s="31" t="inlineStr"/>
+      <c r="F27" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -25468,7 +25548,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -25476,7 +25556,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F28" s="31" t="inlineStr"/>
+      <c r="F28" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -25495,7 +25579,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -25503,7 +25587,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F29" s="31" t="inlineStr"/>
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -25522,12 +25610,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>Opus</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22.0x</t>
         </is>
       </c>
       <c r="F30" s="31" t="inlineStr"/>
@@ -25549,7 +25637,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -25557,7 +25645,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="31" t="inlineStr"/>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -25576,7 +25668,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">

--- a/dcf/GTLB.xlsx
+++ b/dcf/GTLB.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>32.06999969482422</v>
+        <v>33.65000152587891</v>
       </c>
     </row>
     <row r="14">
@@ -24534,7 +24534,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>32.06999969482422</v>
+        <v>33.65000152587891</v>
       </c>
     </row>
     <row r="49">

--- a/dcf/GTLB.xlsx
+++ b/dcf/GTLB.xlsx
@@ -189,8 +189,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1174,182 +1174,182 @@
       <c r="A5" s="52" t="n">
         <v>19</v>
       </c>
-      <c r="B5" s="53" t="n">
-        <v>15.12182549226876</v>
-      </c>
-      <c r="C5" s="53" t="n">
-        <v>14.74146659406419</v>
-      </c>
-      <c r="D5" s="53" t="n">
-        <v>14.38045149220296</v>
-      </c>
-      <c r="E5" s="53" t="n">
-        <v>14.03772501504744</v>
-      </c>
-      <c r="F5" s="53" t="n">
-        <v>13.71229388006082</v>
-      </c>
-      <c r="G5" s="53" t="n">
-        <v>13.4032228052653</v>
-      </c>
-      <c r="H5" s="53" t="n">
-        <v>13.10963088125687</v>
+      <c r="B5" s="8" t="n">
+        <v>41.71505961838782</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>40.25017949306287</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>38.85642121120214</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>37.52998612682848</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>36.2672957974393</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>35.06497824972231</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>33.919855160987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="52" t="n">
         <v>20</v>
       </c>
-      <c r="B6" s="53" t="n">
-        <v>15.54446149250624</v>
-      </c>
-      <c r="C6" s="53" t="n">
-        <v>15.14476402492781</v>
-      </c>
-      <c r="D6" s="53" t="n">
-        <v>14.76537926819877</v>
-      </c>
-      <c r="E6" s="53" t="n">
-        <v>14.40519933318088</v>
-      </c>
-      <c r="F6" s="53" t="n">
-        <v>14.06318131308638</v>
-      </c>
-      <c r="G6" s="53" t="n">
-        <v>13.73834320035646</v>
-      </c>
-      <c r="H6" s="53" t="n">
-        <v>13.4297600771518</v>
+      <c r="B6" s="8" t="n">
+        <v>43.1568220509989</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>41.62597115458964</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>40.16954741528189</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>38.78357234886461</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>37.46429822678116</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>36.20819367806427</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>35.01193025152346</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n">
         <v>21</v>
       </c>
-      <c r="B7" s="53" t="n">
-        <v>15.96709749274372</v>
-      </c>
-      <c r="C7" s="53" t="n">
-        <v>15.54806145579144</v>
-      </c>
-      <c r="D7" s="53" t="n">
-        <v>15.15030704419457</v>
-      </c>
-      <c r="E7" s="53" t="n">
-        <v>14.77267365131432</v>
-      </c>
-      <c r="F7" s="53" t="n">
-        <v>14.41406874611193</v>
-      </c>
-      <c r="G7" s="53" t="n">
-        <v>14.07346359544762</v>
-      </c>
-      <c r="H7" s="53" t="n">
-        <v>13.74988927304674</v>
+      <c r="B7" s="8" t="n">
+        <v>44.59858448361001</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>43.0017628161164</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>41.48267361936166</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>40.03715857090075</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>38.66130065612302</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>37.35140910640624</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>36.10400534205993</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
         <v>22</v>
       </c>
-      <c r="B8" s="53" t="n">
-        <v>16.3897334929812</v>
-      </c>
-      <c r="C8" s="53" t="n">
-        <v>15.95135888665507</v>
-      </c>
-      <c r="D8" s="53" t="n">
-        <v>15.53523482019038</v>
-      </c>
-      <c r="E8" s="54" t="n">
-        <v>15.14014796944775</v>
-      </c>
-      <c r="F8" s="53" t="n">
-        <v>14.76495617913749</v>
-      </c>
-      <c r="G8" s="53" t="n">
-        <v>14.40858399053878</v>
-      </c>
-      <c r="H8" s="53" t="n">
-        <v>14.07001846894167</v>
+      <c r="B8" s="8" t="n">
+        <v>46.0403469162211</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>44.37755447764317</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>42.79579982344141</v>
+      </c>
+      <c r="E8" s="53" t="n">
+        <v>41.29074479293688</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>39.85830308546487</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>38.4946245347482</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>37.1960804325964</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
         <v>23</v>
       </c>
-      <c r="B9" s="53" t="n">
-        <v>16.81236949321868</v>
-      </c>
-      <c r="C9" s="53" t="n">
-        <v>16.35465631751869</v>
-      </c>
-      <c r="D9" s="53" t="n">
-        <v>15.92016259618618</v>
-      </c>
-      <c r="E9" s="53" t="n">
-        <v>15.50762228758119</v>
-      </c>
-      <c r="F9" s="53" t="n">
-        <v>15.11584361216304</v>
-      </c>
-      <c r="G9" s="53" t="n">
-        <v>14.74370438562994</v>
-      </c>
-      <c r="H9" s="53" t="n">
-        <v>14.3901476648366</v>
+      <c r="B9" s="8" t="n">
+        <v>47.4821093488322</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>45.75334613916992</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>44.10892602752116</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>42.54433101497302</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>41.05530551480672</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>39.63783996309017</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>38.28815552313286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
         <v>24</v>
       </c>
-      <c r="B10" s="53" t="n">
-        <v>17.23500549345616</v>
-      </c>
-      <c r="C10" s="53" t="n">
-        <v>16.75795374838232</v>
-      </c>
-      <c r="D10" s="53" t="n">
-        <v>16.30509037218199</v>
-      </c>
-      <c r="E10" s="53" t="n">
-        <v>15.87509660571462</v>
-      </c>
-      <c r="F10" s="53" t="n">
-        <v>15.4667310451886</v>
-      </c>
-      <c r="G10" s="53" t="n">
-        <v>15.0788247807211</v>
-      </c>
-      <c r="H10" s="53" t="n">
-        <v>14.71027686073154</v>
+      <c r="B10" s="8" t="n">
+        <v>48.92387178144328</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>47.12913780069668</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>45.42205223160092</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>43.79791723700916</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>42.25230794414858</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>40.78105539143213</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>39.38023061366932</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
         <v>25</v>
       </c>
-      <c r="B11" s="53" t="n">
-        <v>17.65764149369364</v>
-      </c>
-      <c r="C11" s="53" t="n">
-        <v>17.16125117924595</v>
-      </c>
-      <c r="D11" s="53" t="n">
-        <v>16.6900181481778</v>
-      </c>
-      <c r="E11" s="53" t="n">
-        <v>16.24257092384806</v>
-      </c>
-      <c r="F11" s="53" t="n">
-        <v>15.81761847821416</v>
-      </c>
-      <c r="G11" s="53" t="n">
-        <v>15.41394517581227</v>
-      </c>
-      <c r="H11" s="53" t="n">
-        <v>15.03040605662648</v>
+      <c r="B11" s="8" t="n">
+        <v>50.36563421405438</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>48.50492946222344</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>46.73517843568067</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>45.05150345904529</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>43.44931037349043</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>41.92427081977409</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>40.47230570420578</v>
       </c>
     </row>
     <row r="13">
@@ -1358,7 +1358,7 @@
           <t>Current price</t>
         </is>
       </c>
-      <c r="B13" s="53" t="n">
+      <c r="B13" s="54" t="n">
         <v>33.65000152587891</v>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.3512926050206785</v>
+        <v>0.704980686195141</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24339,7 +24339,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>0.172039768372353</v>
+        <v>0.25</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -24696,13 +24696,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>15.14014796944775</v>
+        <v>41.29074479293688</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>23.64937247133113</v>
+        <v>56.93573124452011</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>9.459963066721421</v>
+        <v>29.90216749832541</v>
       </c>
     </row>
     <row r="59">
@@ -24772,7 +24772,7 @@
         </is>
       </c>
       <c r="B65" s="15" t="n">
-        <v>0.22502679999665</v>
+        <v>0.18</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         </is>
       </c>
       <c r="B66" s="15" t="n">
-        <v>0.13501607999799</v>
+        <v>0.1</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
